--- a/2.Hardware/1.PCB/2.HBridge/2.HBridgeDriver/6.BOM/BOMHBridgeDriver.xlsx
+++ b/2.Hardware/1.PCB/2.HBridge/2.HBridgeDriver/6.BOM/BOMHBridgeDriver.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>Name</t>
   </si>
@@ -56,7 +56,7 @@
     <t>C1, C2</t>
   </si>
   <si>
-    <t>0108051031050</t>
+    <t>https://www.thegioiic.com/tu-gom-0603-22uf-10v</t>
   </si>
   <si>
     <t>CAP, size 0805, 10 nF, 50 VDC</t>
@@ -65,13 +65,22 @@
     <t>C3</t>
   </si>
   <si>
-    <t>1N5819W</t>
+    <t>https://www.thegioiic.com/tu-gom-0805-10nf-50v</t>
+  </si>
+  <si>
+    <t>Diode 1N5819W</t>
+  </si>
+  <si>
+    <t>1N5819W Diode Schottky 1A 40V SOD-123</t>
   </si>
   <si>
     <t>D1, D2</t>
   </si>
   <si>
-    <t>160603GreenClear</t>
+    <t>https://www.thegioiic.com/1n5819w-diode-schottky-1a-40v-sod-123</t>
+  </si>
+  <si>
+    <t>LED xanh lá</t>
   </si>
   <si>
     <t>WL-SMCW SMT Mono-color Chip LED Waterclear, size 0603, Green, 3.2V, 140deg</t>
@@ -80,7 +89,10 @@
     <t>D3</t>
   </si>
   <si>
-    <t>160603BlueClear</t>
+    <t>https://www.thegioiic.com/led-xanh-la-0603-dan-smd-trong-suot</t>
+  </si>
+  <si>
+    <t>LED xanh dương</t>
   </si>
   <si>
     <t>WL-SMCW SMT Mono-color Chip LED Waterclear, size 0603, Blue, 3.2V, 140deg</t>
@@ -89,40 +101,55 @@
     <t>D4</t>
   </si>
   <si>
-    <t>KF301-2P</t>
+    <t>https://www.thegioiic.com/led-xanh-duong-0603-dan-smd-trong-suot</t>
   </si>
   <si>
     <t>2 Pin Terminal Block 5mm Pitch</t>
   </si>
   <si>
+    <t>KF301-2-V Domino 2 Chân Thẳng 5.08mm 300V 10A Hàn PCB</t>
+  </si>
+  <si>
     <t>J1</t>
   </si>
   <si>
-    <t>KF120-2</t>
+    <t>https://www.thegioiic.com/kf301-2-v-domino-2-chan-thang-5-08mm-300v-10a-han-pcb</t>
   </si>
   <si>
     <t>2.54mm Terminal</t>
   </si>
   <si>
+    <t>KF120-2-V Domino 2 Chân Thẳng 2.54mm 150V 6A Hàn PCB</t>
+  </si>
+  <si>
     <t>J2, J3</t>
   </si>
   <si>
-    <t>90StraightHeader</t>
+    <t>https://www.thegioiic.com/kf120-2-v-domino-2-chan-thang-2-54mm-150v-6a-han-pcb</t>
+  </si>
+  <si>
+    <t>Hàng Rào Đực Đôi 2.54mm</t>
+  </si>
+  <si>
+    <t>Hàng Rào Đực Đôi 2.54mm 80 Chân 2 Hàng Cao 21mm Xuyên Lỗ</t>
   </si>
   <si>
     <t>J4</t>
   </si>
   <si>
-    <t>IRLR7843TRPBF</t>
-  </si>
-  <si>
-    <t>RoHS Compliant</t>
+    <t>https://www.thegioiic.com/hang-rao-duc-doi-2-54mm-80-chan-2-hang-cao-21mm-xuyen-lo</t>
+  </si>
+  <si>
+    <t>IRLR7843</t>
+  </si>
+  <si>
+    <t>IRLR7843 MOSFET Kênh N 30V 161A TO-252-3</t>
   </si>
   <si>
     <t>Q1, Q2, Q3, Q4</t>
   </si>
   <si>
-    <t>0006031011</t>
+    <t>https://www.thegioiic.com/irlr7843-mosfet-kenh-n-30v-161a-to-252-3</t>
   </si>
   <si>
     <t>RES, size 0603, 100 Ohm, 1/4 W</t>
@@ -131,7 +158,7 @@
     <t>R1, R4, R5, R6, R9, R10</t>
   </si>
   <si>
-    <t>0006031021</t>
+    <t>https://www.thegioiic.com/dien-tro-100-ohm-0603-1-</t>
   </si>
   <si>
     <t>RES, size 0603, 1 KOhm, 1/4 W</t>
@@ -140,7 +167,7 @@
     <t>R2, R3, R13</t>
   </si>
   <si>
-    <t>0006031031</t>
+    <t>https://www.thegioiic.com/dien-tro-1-kohm-0603-5-</t>
   </si>
   <si>
     <t>RES, size 0603, 10 KOhm, 1/4 W</t>
@@ -149,13 +176,19 @@
     <t>R7, R8, R11, R12</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/dien-tro-10-kohm-0603-5-</t>
+  </si>
+  <si>
     <t>MP3.2</t>
   </si>
   <si>
     <t>Scr1</t>
   </si>
   <si>
-    <t>PC817X2NIP1B</t>
+    <t>https://www.thegioiic.com/vit-nhua-m3-dai-5mm</t>
+  </si>
+  <si>
+    <t>PC817X2NIPW</t>
   </si>
   <si>
     <t>Optocoupler DC-IN 1-CH Transistor DC-OUT 4-Pin DIP SMD T/R</t>
@@ -164,6 +197,9 @@
     <t>U1, U4</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/pc817x2nipw-optoisolator-transistor-output-5000vrms-1-channel-sop-4</t>
+  </si>
+  <si>
     <t>IR2104SPBF</t>
   </si>
   <si>
@@ -171,19 +207,33 @@
   </si>
   <si>
     <t>U2, U3</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/ir2104spbf-mosfet-2-ngo-ra-360-ma-20v-8-soic</t>
+  </si>
+  <si>
+    <t>PCB</t>
+  </si>
+  <si>
+    <t>PCB-Pannel</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ [$VND]\ * #,##0.00_ ;_ [$VND]\ * \-#,##0.00_ ;_ [$VND]\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="[$VND]\ #,##0.00;[$VND]\ \-#,##0.00"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -192,11 +242,42 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF467886"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -656,141 +737,159 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1326,239 +1425,417 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="17.6666666666667" customWidth="1"/>
     <col min="2" max="2" width="74.4444444444444" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="5" max="5" width="15.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="15.5555555555556" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
-        <v>10603226106.3</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <v>2</v>
       </c>
+      <c r="E2" s="3">
+        <v>550</v>
+      </c>
+      <c r="F2" s="3">
+        <v>5500</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <v>1</v>
       </c>
+      <c r="E3" s="3">
+        <v>190</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
+    <row r="4" spans="1:7">
+      <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4">
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2">
         <v>2</v>
       </c>
+      <c r="E4" s="3">
+        <v>350</v>
+      </c>
+      <c r="F4" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5">
+    <row r="5" spans="1:7">
+      <c r="A5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="2">
         <v>1</v>
       </c>
+      <c r="E5" s="3">
+        <v>190</v>
+      </c>
+      <c r="F5" s="3">
+        <v>190</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6">
+    <row r="6" spans="1:7">
+      <c r="A6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="2">
         <v>1</v>
       </c>
+      <c r="E6" s="3">
+        <v>170</v>
+      </c>
+      <c r="F6" s="3">
+        <v>170</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7">
+    <row r="7" spans="1:7">
+      <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="2">
         <v>1</v>
       </c>
+      <c r="E7" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8">
+    <row r="8" spans="1:7">
+      <c r="A8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="2">
         <v>2</v>
       </c>
+      <c r="E8" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9">
+    <row r="9" spans="1:7">
+      <c r="A9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="2">
         <v>1</v>
       </c>
+      <c r="E9" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>4000</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10">
+    <row r="10" spans="1:7">
+      <c r="A10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="2">
         <v>4</v>
       </c>
+      <c r="E10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>12000</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" t="s">
+    <row r="11" spans="1:7">
+      <c r="A11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="2">
+        <v>6</v>
+      </c>
+      <c r="E11" s="3">
+        <v>38</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="2">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3">
         <v>32</v>
       </c>
-      <c r="C11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11">
-        <v>6</v>
+      <c r="F12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12">
+    <row r="13" spans="1:7">
+      <c r="A13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="2">
+        <v>4</v>
+      </c>
+      <c r="E13" s="3">
         <v>3</v>
       </c>
+      <c r="F13" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
+      <c r="E14" s="5">
+        <v>380</v>
+      </c>
+      <c r="F14" s="5">
+        <f>E14*D14</f>
+        <v>380</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15">
+    <row r="15" spans="1:7">
+      <c r="A15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="2">
         <v>2</v>
       </c>
+      <c r="E15" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F15" s="3">
+        <v>5600</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16">
+    <row r="16" spans="1:7">
+      <c r="A16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="2">
         <v>2</v>
+      </c>
+      <c r="E16" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F16" s="3">
+        <v>30000</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17">
+        <v>5</v>
+      </c>
+      <c r="E17" s="7">
+        <v>20</v>
+      </c>
+      <c r="F17" s="7">
+        <f>E17*D17</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="5:6">
+      <c r="E18" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F18" s="9">
+        <f>SUM(F2:F17)-4*E17</f>
+        <v>72860</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" display="https://www.thegioiic.com/tu-gom-0603-22uf-10v" tooltip="https://www.thegioiic.com/tu-gom-0603-22uf-10v"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://www.thegioiic.com/tu-gom-0805-10nf-50v" tooltip="https://www.thegioiic.com/tu-gom-0805-10nf-50v"/>
+    <hyperlink ref="G4" r:id="rId3" display="https://www.thegioiic.com/1n5819w-diode-schottky-1a-40v-sod-123" tooltip="https://www.thegioiic.com/1n5819w-diode-schottky-1a-40v-sod-123"/>
+    <hyperlink ref="G5" r:id="rId4" display="https://www.thegioiic.com/led-xanh-la-0603-dan-smd-trong-suot" tooltip="https://www.thegioiic.com/led-xanh-la-0603-dan-smd-trong-suot"/>
+    <hyperlink ref="G6" r:id="rId5" display="https://www.thegioiic.com/led-xanh-duong-0603-dan-smd-trong-suot" tooltip="https://www.thegioiic.com/led-xanh-duong-0603-dan-smd-trong-suot"/>
+    <hyperlink ref="G7" r:id="rId6" display="https://www.thegioiic.com/kf301-2-v-domino-2-chan-thang-5-08mm-300v-10a-han-pcb" tooltip="https://www.thegioiic.com/kf301-2-v-domino-2-chan-thang-5-08mm-300v-10a-han-pcb"/>
+    <hyperlink ref="G8" r:id="rId7" display="https://www.thegioiic.com/kf120-2-v-domino-2-chan-thang-2-54mm-150v-6a-han-pcb" tooltip="https://www.thegioiic.com/kf120-2-v-domino-2-chan-thang-2-54mm-150v-6a-han-pcb"/>
+    <hyperlink ref="G9" r:id="rId8" display="https://www.thegioiic.com/hang-rao-duc-doi-2-54mm-80-chan-2-hang-cao-21mm-xuyen-lo" tooltip="https://www.thegioiic.com/hang-rao-duc-doi-2-54mm-80-chan-2-hang-cao-21mm-xuyen-lo"/>
+    <hyperlink ref="G10" r:id="rId9" display="https://www.thegioiic.com/irlr7843-mosfet-kenh-n-30v-161a-to-252-3" tooltip="https://www.thegioiic.com/irlr7843-mosfet-kenh-n-30v-161a-to-252-3"/>
+    <hyperlink ref="G11" r:id="rId10" display="https://www.thegioiic.com/dien-tro-100-ohm-0603-1-" tooltip="https://www.thegioiic.com/dien-tro-100-ohm-0603-1-"/>
+    <hyperlink ref="G12" r:id="rId11" display="https://www.thegioiic.com/dien-tro-1-kohm-0603-5-" tooltip="https://www.thegioiic.com/dien-tro-1-kohm-0603-5-"/>
+    <hyperlink ref="G13" r:id="rId12" display="https://www.thegioiic.com/dien-tro-10-kohm-0603-5-" tooltip="https://www.thegioiic.com/dien-tro-10-kohm-0603-5-"/>
+    <hyperlink ref="G15" r:id="rId13" display="https://www.thegioiic.com/pc817x2nipw-optoisolator-transistor-output-5000vrms-1-channel-sop-4" tooltip="https://www.thegioiic.com/pc817x2nipw-optoisolator-transistor-output-5000vrms-1-channel-sop-4"/>
+    <hyperlink ref="G16" r:id="rId14" display="https://www.thegioiic.com/ir2104spbf-mosfet-2-ngo-ra-360-ma-20v-8-soic" tooltip="https://www.thegioiic.com/ir2104spbf-mosfet-2-ngo-ra-360-ma-20v-8-soic"/>
+    <hyperlink ref="G14" r:id="rId15" display="https://www.thegioiic.com/vit-nhua-m3-dai-5mm"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
